--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>STT</t>
   </si>
@@ -42,19 +42,34 @@
     <t>folder_video</t>
   </si>
   <si>
+    <t>video_name</t>
+  </si>
+  <si>
     <t>result</t>
   </si>
   <si>
     <t>manh test 1</t>
   </si>
   <si>
+    <t>a4ebeb4c-eb5c-41f3-b1ed-dff9814983a3</t>
+  </si>
+  <si>
     <t>proxy1</t>
   </si>
   <si>
     <t>E:\Youtube\Short\Video-up\Kênh 1\New\4</t>
   </si>
   <si>
-    <t xml:space="preserve"> babc7efc-5629-489e-bff8-c814b98ff494</t>
+    <t>grok_job130_8a35d</t>
+  </si>
+  <si>
+    <t>manh test 2</t>
+  </si>
+  <si>
+    <t>5/30/2026  16:00:00 AM</t>
+  </si>
+  <si>
+    <t>grok_job131_fa880</t>
   </si>
 </sst>
 </file>
@@ -92,7 +107,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -156,10 +171,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -191,10 +206,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -432,14 +447,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="34.375" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="7" max="8" width="35.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,34 +481,66 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46162.333333333336</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1">
-        <v>46114.25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 A2:C2 F2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I1 A3:I3 A2:H2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>